--- a/database/seeders/data/02_CLUBES_Y_CONFIGURACION.xlsx
+++ b/database/seeders/data/02_CLUBES_Y_CONFIGURACION.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Apache24\htdocs\ParquesEsp\database\seeders\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E24A7C9-3F24-40F2-8989-9393DCD484FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09578445-377A-426F-BA8F-3E2F3FF4F721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INSTRUCCIONES" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="167">
   <si>
     <t>INSTRUCCIONES DE CAPTURA</t>
   </si>
@@ -365,9 +365,6 @@
     <t>Nombre del club</t>
   </si>
   <si>
-    <t>Código corto, ej. PE1</t>
-  </si>
-  <si>
     <t>SÍ/NO</t>
   </si>
   <si>
@@ -410,12 +407,6 @@
     <t>URL de Threads</t>
   </si>
   <si>
-    <t>Nombre/ruta del archivo del logo (se sube aparte)</t>
-  </si>
-  <si>
-    <t>Nombre/ruta del archivo del mapa (se sube aparte)</t>
-  </si>
-  <si>
     <t>NO</t>
   </si>
   <si>
@@ -428,43 +419,10 @@
     <t>2222431070</t>
   </si>
   <si>
-    <t>https://pagina-parqueespana.atxiontech.com/parque-espana-1</t>
-  </si>
-  <si>
-    <t>http://www.parqueespana2.com.mx</t>
-  </si>
-  <si>
-    <t>https://www.whatsapp.com/channel/0029VbAqplVBqbrB1fzv4r3P</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/parqueespana_puebla</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/parqueespanapuebla</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/@parqueespana/videos</t>
-  </si>
-  <si>
-    <t>https://www.threads.com/@parqueespana_puebla?xmt=AQG0M0EUKgaI8QxIa5KJ6BXAhitC13KFnlZrsTEBG_-cwkY</t>
-  </si>
-  <si>
     <t>fatane@parqueespana2.com.mx</t>
   </si>
   <si>
     <t>2222841091</t>
-  </si>
-  <si>
-    <t>https://pagina-parqueespana.atxiontech.com/parque-espana-2</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/parqueespana2</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/parque2</t>
-  </si>
-  <si>
-    <t>https://x.com/parque2</t>
   </si>
   <si>
     <r>
@@ -651,6 +609,15 @@
   <si>
     <t>Último folio usado en esa serie</t>
   </si>
+  <si>
+    <t>Código corto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre/ruta del archivo del mapa </t>
+  </si>
+  <si>
+    <t>Nombre/ruta del archivo del logo</t>
+  </si>
 </sst>
 </file>
 
@@ -660,7 +627,7 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -731,6 +698,12 @@
     <font>
       <sz val="11"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <name val="Carlito"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="14">
@@ -871,7 +844,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -921,13 +894,14 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1773,7 +1747,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="21" t="s">
         <v>103</v>
       </c>
       <c r="B1" s="22"/>
@@ -1855,55 +1829,55 @@
         <v>104</v>
       </c>
       <c r="B3" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="C3" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="D3" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="E3" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="F3" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="G3" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="H3" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="I3" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="I3" s="14" t="s">
+      <c r="J3" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="J3" s="14" t="s">
+      <c r="K3" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="K3" s="14" t="s">
+      <c r="L3" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="L3" s="14" t="s">
+      <c r="M3" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="M3" s="14" t="s">
+      <c r="N3" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="N3" s="14" t="s">
+      <c r="O3" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="O3" s="14" t="s">
+      <c r="P3" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="P3" s="14" t="s">
-        <v>119</v>
-      </c>
       <c r="Q3" s="14" t="s">
-        <v>120</v>
+        <v>166</v>
       </c>
       <c r="R3" s="14" t="s">
-        <v>121</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
@@ -1917,38 +1891,18 @@
         <v>40</v>
       </c>
       <c r="D4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F4" t="s">
+        <v>121</v>
+      </c>
+      <c r="H4" t="s">
         <v>122</v>
       </c>
-      <c r="E4" t="s">
-        <v>123</v>
-      </c>
-      <c r="F4" t="s">
-        <v>124</v>
-      </c>
-      <c r="H4" t="s">
-        <v>125</v>
-      </c>
-      <c r="I4" t="s">
-        <v>126</v>
-      </c>
-      <c r="J4" t="s">
-        <v>127</v>
-      </c>
-      <c r="K4" t="s">
-        <v>128</v>
-      </c>
-      <c r="L4" t="s">
-        <v>129</v>
-      </c>
-      <c r="M4" t="s">
-        <v>130</v>
-      </c>
-      <c r="N4" t="s">
-        <v>131</v>
-      </c>
-      <c r="P4" t="s">
-        <v>132</v>
-      </c>
+      <c r="M4" s="24"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
@@ -1964,34 +1918,16 @@
         <v>40</v>
       </c>
       <c r="E5" t="s">
+        <v>120</v>
+      </c>
+      <c r="F5" t="s">
+        <v>121</v>
+      </c>
+      <c r="G5" t="s">
         <v>123</v>
       </c>
-      <c r="F5" t="s">
+      <c r="H5" t="s">
         <v>124</v>
-      </c>
-      <c r="G5" t="s">
-        <v>133</v>
-      </c>
-      <c r="H5" t="s">
-        <v>134</v>
-      </c>
-      <c r="I5" t="s">
-        <v>135</v>
-      </c>
-      <c r="J5" t="s">
-        <v>127</v>
-      </c>
-      <c r="L5" t="s">
-        <v>136</v>
-      </c>
-      <c r="M5" t="s">
-        <v>137</v>
-      </c>
-      <c r="O5" t="s">
-        <v>138</v>
-      </c>
-      <c r="P5" t="s">
-        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -1999,6 +1935,7 @@
     <mergeCell ref="A1:R1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="146" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2017,8 +1954,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="21" t="s">
-        <v>139</v>
+      <c r="A1" s="23" t="s">
+        <v>125</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -2060,31 +1997,31 @@
     </row>
     <row r="3" spans="1:9" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
@@ -2092,22 +2029,22 @@
         <v>38</v>
       </c>
       <c r="B4" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="C4" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="F4" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="G4" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="H4" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="I4" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
@@ -2115,22 +2052,22 @@
         <v>51</v>
       </c>
       <c r="B5" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="E5" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="F5" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="G5" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="H5" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="I5" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -2154,8 +2091,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="21" t="s">
-        <v>158</v>
+      <c r="A1" s="23" t="s">
+        <v>144</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -2176,24 +2113,24 @@
         <v>87</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -2201,7 +2138,7 @@
         <v>38</v>
       </c>
       <c r="B4" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="C4" t="s">
         <v>40</v>
@@ -2215,7 +2152,7 @@
         <v>38</v>
       </c>
       <c r="B5" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="C5" t="s">
         <v>40</v>
@@ -2229,7 +2166,7 @@
         <v>38</v>
       </c>
       <c r="B6" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="C6" t="s">
         <v>40</v>
@@ -2243,7 +2180,7 @@
         <v>38</v>
       </c>
       <c r="B7" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C7" t="s">
         <v>40</v>
@@ -2257,7 +2194,7 @@
         <v>38</v>
       </c>
       <c r="B8" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="C8" t="s">
         <v>40</v>
@@ -2271,7 +2208,7 @@
         <v>38</v>
       </c>
       <c r="B9" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="C9" t="s">
         <v>40</v>
@@ -2285,7 +2222,7 @@
         <v>51</v>
       </c>
       <c r="B10" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="C10" t="s">
         <v>40</v>
@@ -2299,7 +2236,7 @@
         <v>51</v>
       </c>
       <c r="B11" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="C11" t="s">
         <v>40</v>
@@ -2313,7 +2250,7 @@
         <v>51</v>
       </c>
       <c r="B12" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="C12" t="s">
         <v>40</v>
@@ -2327,7 +2264,7 @@
         <v>51</v>
       </c>
       <c r="B13" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C13" t="s">
         <v>40</v>
@@ -2341,7 +2278,7 @@
         <v>51</v>
       </c>
       <c r="B14" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="C14" t="s">
         <v>40</v>
@@ -2355,7 +2292,7 @@
         <v>51</v>
       </c>
       <c r="B15" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="C15" t="s">
         <v>40</v>
@@ -2385,8 +2322,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="21" t="s">
-        <v>169</v>
+      <c r="A1" s="23" t="s">
+        <v>155</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -2412,19 +2349,19 @@
     </row>
     <row r="3" spans="1:5" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -2448,8 +2385,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="21" t="s">
-        <v>173</v>
+      <c r="A1" s="23" t="s">
+        <v>159</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -2475,19 +2412,19 @@
     </row>
     <row r="3" spans="1:5" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
